--- a/Data/Results/From Clean Raw Data/Step 3_2026 Format/SIC Codes Consistency Check_Hindu_08.15.2026.xlsx
+++ b/Data/Results/From Clean Raw Data/Step 3_2026 Format/SIC Codes Consistency Check_Hindu_08.15.2026.xlsx
@@ -1,10 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="10419"/>
   <workbookPr defaultThemeVersion="124226"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/sg2736/Desktop/DSDE/Projects/YSPH-DSDE Repos/Yusufs Church Closures/Church-Closures-Dashboard/Data/Results/From Clean Raw Data/Step 3_2026 Format/"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E7FBA84D-89DA-554B-B230-D2E1C1ECB122}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660"/>
+    <workbookView xWindow="240" yWindow="660" windowWidth="16100" windowHeight="9660" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="primary_pct100" sheetId="1" r:id="rId1"/>
@@ -12,22 +18,28 @@
     <sheet name="overflow_pct100" sheetId="3" r:id="rId3"/>
     <sheet name="overflow_pctlt100" sheetId="4" r:id="rId4"/>
   </sheets>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <calcPr calcId="124519"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="34" uniqueCount="15">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="64" uniqueCount="22">
   <si>
     <t>x</t>
   </si>
   <si>
+    <t>classifier</t>
+  </si>
+  <si>
     <t>Freq</t>
   </si>
   <si>
     <t>TEMPLES-HINDU</t>
   </si>
   <si>
+    <t>Hindu Mandir</t>
+  </si>
+  <si>
     <t>ASHRAMS</t>
   </si>
   <si>
@@ -37,15 +49,27 @@
     <t>CHURCHES</t>
   </si>
   <si>
+    <t>Christian Church; Interfaith</t>
+  </si>
+  <si>
     <t>SYNAGOGUES</t>
   </si>
   <si>
+    <t>Jewish Synagogue</t>
+  </si>
+  <si>
     <t>RELIGIOUS ORGANIZATIONS</t>
   </si>
   <si>
+    <t>Interfaith</t>
+  </si>
+  <si>
     <t>TEMPLES-BUDDHIST</t>
   </si>
   <si>
+    <t>Buddhist Temple</t>
+  </si>
+  <si>
     <t>RELIGION OTHER PLACES OF WORSHIP</t>
   </si>
   <si>
@@ -59,6 +83,9 @@
   </si>
   <si>
     <t>SPIRITUAL ORGANIZATIONS</t>
+  </si>
+  <si>
+    <t>Other Religion</t>
   </si>
   <si>
     <t>SYNAGOGUES JEWISH</t>
@@ -67,8 +94,8 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -116,13 +143,21 @@
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2007 - 2010">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -160,7 +195,7 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2007 - 2010">
       <a:majorFont>
         <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
@@ -194,6 +229,7 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri"/>
@@ -228,9 +264,10 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2007 - 2010">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -403,40 +440,55 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B4"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:C4"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="2" max="2" width="11.6640625" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:2" s="1" customFormat="1">
+    <row r="1" spans="1:3" s="1" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="2" spans="1:2">
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
-        <v>2</v>
-      </c>
-      <c r="B2">
-        <v>0.857</v>
-      </c>
-    </row>
-    <row r="3" spans="1:2">
+        <v>3</v>
+      </c>
+      <c r="B2" t="s">
+        <v>4</v>
+      </c>
+      <c r="C2">
+        <v>0.85699999999999998</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
-        <v>3</v>
-      </c>
-      <c r="B3">
-        <v>0.08599999999999999</v>
-      </c>
-    </row>
-    <row r="4" spans="1:2">
+        <v>5</v>
+      </c>
+      <c r="B3" t="s">
+        <v>4</v>
+      </c>
+      <c r="C3">
+        <v>8.5999999999999993E-2</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
+        <v>6</v>
+      </c>
+      <c r="B4" t="s">
         <v>4</v>
       </c>
-      <c r="B4">
-        <v>0.057</v>
+      <c r="C4">
+        <v>5.7000000000000002E-2</v>
       </c>
     </row>
   </sheetData>
@@ -445,56 +497,77 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B6"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
+  <dimension ref="A1:C6"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="1" max="2" width="22.1640625" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:2" s="1" customFormat="1">
+    <row r="1" spans="1:3" s="1" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="2" spans="1:2">
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
-        <v>5</v>
-      </c>
-      <c r="B2">
+        <v>7</v>
+      </c>
+      <c r="B2" t="s">
+        <v>8</v>
+      </c>
+      <c r="C2">
         <v>0.435</v>
       </c>
     </row>
-    <row r="3" spans="1:2">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
-        <v>2</v>
-      </c>
-      <c r="B3">
+        <v>3</v>
+      </c>
+      <c r="B3" t="s">
+        <v>4</v>
+      </c>
+      <c r="C3">
         <v>0.435</v>
       </c>
     </row>
-    <row r="4" spans="1:2">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
-        <v>6</v>
-      </c>
-      <c r="B4">
-        <v>0.08699999999999999</v>
-      </c>
-    </row>
-    <row r="5" spans="1:2">
+        <v>9</v>
+      </c>
+      <c r="B4" t="s">
+        <v>10</v>
+      </c>
+      <c r="C4">
+        <v>8.6999999999999994E-2</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
-        <v>7</v>
-      </c>
-      <c r="B5">
-        <v>0.022</v>
-      </c>
-    </row>
-    <row r="6" spans="1:2">
+        <v>11</v>
+      </c>
+      <c r="B5" t="s">
+        <v>12</v>
+      </c>
+      <c r="C5">
+        <v>2.1999999999999999E-2</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
-        <v>8</v>
-      </c>
-      <c r="B6">
-        <v>0.022</v>
+        <v>13</v>
+      </c>
+      <c r="B6" t="s">
+        <v>14</v>
+      </c>
+      <c r="C6">
+        <v>2.1999999999999999E-2</v>
       </c>
     </row>
   </sheetData>
@@ -503,56 +576,74 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B6"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
+  <dimension ref="A1:C6"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <sheetData>
-    <row r="1" spans="1:2" s="1" customFormat="1">
+    <row r="1" spans="1:3" s="1" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="2" spans="1:2">
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
+        <v>7</v>
+      </c>
+      <c r="B2" t="s">
+        <v>8</v>
+      </c>
+      <c r="C2">
+        <v>0.47599999999999998</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A3" t="s">
+        <v>9</v>
+      </c>
+      <c r="B3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C3">
+        <v>0.23799999999999999</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A4" t="s">
+        <v>11</v>
+      </c>
+      <c r="B4" t="s">
+        <v>12</v>
+      </c>
+      <c r="C4">
+        <v>0.19</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A5" t="s">
         <v>5</v>
       </c>
-      <c r="B2">
-        <v>0.476</v>
-      </c>
-    </row>
-    <row r="3" spans="1:2">
-      <c r="A3" t="s">
-        <v>6</v>
-      </c>
-      <c r="B3">
-        <v>0.238</v>
-      </c>
-    </row>
-    <row r="4" spans="1:2">
-      <c r="A4" t="s">
-        <v>7</v>
-      </c>
-      <c r="B4">
-        <v>0.19</v>
-      </c>
-    </row>
-    <row r="5" spans="1:2">
-      <c r="A5" t="s">
-        <v>3</v>
-      </c>
-      <c r="B5">
-        <v>0.048</v>
-      </c>
-    </row>
-    <row r="6" spans="1:2">
+      <c r="B5" t="s">
+        <v>4</v>
+      </c>
+      <c r="C5">
+        <v>4.8000000000000001E-2</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
-        <v>9</v>
-      </c>
-      <c r="B6">
-        <v>0.048</v>
+        <v>15</v>
+      </c>
+      <c r="B6" t="s">
+        <v>12</v>
+      </c>
+      <c r="C6">
+        <v>4.8000000000000001E-2</v>
       </c>
     </row>
   </sheetData>
@@ -561,120 +652,162 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B14"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
+  <dimension ref="A1:C14"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <sheetData>
-    <row r="1" spans="1:2" s="1" customFormat="1">
+    <row r="1" spans="1:3" s="1" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="2" spans="1:2">
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
-        <v>2</v>
-      </c>
-      <c r="B2">
-        <v>0.359</v>
-      </c>
-    </row>
-    <row r="3" spans="1:2">
+        <v>3</v>
+      </c>
+      <c r="B2" t="s">
+        <v>4</v>
+      </c>
+      <c r="C2">
+        <v>0.35899999999999999</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
+        <v>7</v>
+      </c>
+      <c r="B3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C3">
+        <v>0.34599999999999997</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A4" t="s">
+        <v>9</v>
+      </c>
+      <c r="B4" t="s">
+        <v>10</v>
+      </c>
+      <c r="C4">
+        <v>0.185</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A5" t="s">
+        <v>11</v>
+      </c>
+      <c r="B5" t="s">
+        <v>12</v>
+      </c>
+      <c r="C5">
+        <v>5.1999999999999998E-2</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A6" t="s">
+        <v>6</v>
+      </c>
+      <c r="B6" t="s">
+        <v>4</v>
+      </c>
+      <c r="C6">
+        <v>2.8000000000000001E-2</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A7" t="s">
         <v>5</v>
       </c>
-      <c r="B3">
-        <v>0.346</v>
-      </c>
-    </row>
-    <row r="4" spans="1:2">
-      <c r="A4" t="s">
-        <v>6</v>
-      </c>
-      <c r="B4">
-        <v>0.185</v>
-      </c>
-    </row>
-    <row r="5" spans="1:2">
-      <c r="A5" t="s">
-        <v>7</v>
-      </c>
-      <c r="B5">
-        <v>0.052</v>
-      </c>
-    </row>
-    <row r="6" spans="1:2">
-      <c r="A6" t="s">
+      <c r="B7" t="s">
         <v>4</v>
       </c>
-      <c r="B6">
-        <v>0.028</v>
-      </c>
-    </row>
-    <row r="7" spans="1:2">
-      <c r="A7" t="s">
-        <v>3</v>
-      </c>
-      <c r="B7">
-        <v>0.013</v>
-      </c>
-    </row>
-    <row r="8" spans="1:2">
+      <c r="C7">
+        <v>1.2999999999999999E-2</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
+        <v>16</v>
+      </c>
+      <c r="B8" t="s">
+        <v>8</v>
+      </c>
+      <c r="C8">
+        <v>3.0000000000000001E-3</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A9" t="s">
+        <v>17</v>
+      </c>
+      <c r="B9" t="s">
+        <v>12</v>
+      </c>
+      <c r="C9">
+        <v>3.0000000000000001E-3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A10" t="s">
+        <v>13</v>
+      </c>
+      <c r="B10" t="s">
+        <v>14</v>
+      </c>
+      <c r="C10">
+        <v>3.0000000000000001E-3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A11" t="s">
+        <v>18</v>
+      </c>
+      <c r="B11" t="s">
+        <v>12</v>
+      </c>
+      <c r="C11">
+        <v>2E-3</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A12" t="s">
+        <v>15</v>
+      </c>
+      <c r="B12" t="s">
+        <v>12</v>
+      </c>
+      <c r="C12">
+        <v>2E-3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A13" t="s">
+        <v>19</v>
+      </c>
+      <c r="B13" t="s">
+        <v>20</v>
+      </c>
+      <c r="C13">
+        <v>2E-3</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A14" t="s">
+        <v>21</v>
+      </c>
+      <c r="B14" t="s">
         <v>10</v>
       </c>
-      <c r="B8">
-        <v>0.003</v>
-      </c>
-    </row>
-    <row r="9" spans="1:2">
-      <c r="A9" t="s">
-        <v>11</v>
-      </c>
-      <c r="B9">
-        <v>0.003</v>
-      </c>
-    </row>
-    <row r="10" spans="1:2">
-      <c r="A10" t="s">
-        <v>8</v>
-      </c>
-      <c r="B10">
-        <v>0.003</v>
-      </c>
-    </row>
-    <row r="11" spans="1:2">
-      <c r="A11" t="s">
-        <v>12</v>
-      </c>
-      <c r="B11">
-        <v>0.002</v>
-      </c>
-    </row>
-    <row r="12" spans="1:2">
-      <c r="A12" t="s">
-        <v>9</v>
-      </c>
-      <c r="B12">
-        <v>0.002</v>
-      </c>
-    </row>
-    <row r="13" spans="1:2">
-      <c r="A13" t="s">
-        <v>13</v>
-      </c>
-      <c r="B13">
-        <v>0.002</v>
-      </c>
-    </row>
-    <row r="14" spans="1:2">
-      <c r="A14" t="s">
-        <v>14</v>
-      </c>
-      <c r="B14">
-        <v>0.002</v>
+      <c r="C14">
+        <v>2E-3</v>
       </c>
     </row>
   </sheetData>
